--- a/Scoring Logic and Documentation/method/weight_discrimination.xlsx
+++ b/Scoring Logic and Documentation/method/weight_discrimination.xlsx
@@ -508,10 +508,10 @@
         <v>0.0635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2512</v>
+        <v>0.251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0488</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="3">
@@ -549,10 +549,10 @@
         <v>0.0503</v>
       </c>
       <c r="J3" t="n">
-        <v>0.199</v>
+        <v>0.1988</v>
       </c>
       <c r="K3" t="n">
-        <v>0.151</v>
+        <v>0.1512</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4265</v>
+        <v>0.4275</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0853</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3374</v>
+        <v>0.3379</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1374</v>
+        <v>-0.1379</v>
       </c>
     </row>
     <row r="5">
@@ -631,10 +631,10 @@
         <v>0.0537</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2124</v>
+        <v>0.2122</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0624</v>
+        <v>-0.0622</v>
       </c>
     </row>
     <row r="6">
@@ -1000,10 +1000,10 @@
         <v>0.108</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3014</v>
+        <v>0.3007</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0014</v>
+        <v>-0.0007</v>
       </c>
     </row>
     <row r="15">
@@ -1041,10 +1041,10 @@
         <v>0.1281</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3575</v>
+        <v>0.3567</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0075</v>
+        <v>-0.0067</v>
       </c>
     </row>
     <row r="16">
@@ -1073,19 +1073,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3442</v>
+        <v>0.3481</v>
       </c>
       <c r="H16" t="n">
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0688</v>
+        <v>0.0696</v>
       </c>
       <c r="J16" t="n">
-        <v>0.192</v>
+        <v>0.1938</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="17">
@@ -1123,10 +1123,10 @@
         <v>0.0535</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1493</v>
+        <v>0.149</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>
